--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run2/epoch_150/per_file_predictions_epoch_150.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run2/epoch_150/per_file_predictions_epoch_150.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="494">
   <si>
     <t>Filename</t>
   </si>
@@ -808,685 +808,694 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9598,0.0137,0.0031,0.0024</t>
-  </si>
-  <si>
-    <t>0.0041,0.0000,0.0000,0.9990</t>
-  </si>
-  <si>
-    <t>0.9961,0.0004,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.0011,0.0019,0.0004,0.9989</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9871,0.0026,0.0028,0.0006</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.9939,0.0007,0.0004,0.0017</t>
+  </si>
+  <si>
+    <t>0.0178,0.0004,0.0010,0.9908</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0001,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9988,0.0015,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9974,0.0002,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0226,0.0005,0.9793,0.0001</t>
+  </si>
+  <si>
+    <t>0.9113,0.0037,0.0476,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.0004,0.9952,0.0006</t>
+  </si>
+  <si>
+    <t>0.9901,0.0002,0.0081,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9989,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8344,0.0029,0.1471,0.0008</t>
+  </si>
+  <si>
+    <t>0.9917,0.0000,0.0082,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0242,0.0004,0.9792,0.0001</t>
+  </si>
+  <si>
+    <t>0.3996,0.0000,0.8243,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.0000,0.9980,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9998,0.0006</t>
+  </si>
+  <si>
+    <t>0.0390,0.9675,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.7719,0.2764,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0026,0.9999,0.0171</t>
+  </si>
+  <si>
+    <t>0.0013,0.9932,0.0102,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0262,0.0042,0.9594,0.0021</t>
+  </si>
+  <si>
+    <t>0.0973,0.9186,0.0034,0.0001</t>
+  </si>
+  <si>
+    <t>0.0023,0.9953,0.0048,0.0000</t>
+  </si>
+  <si>
+    <t>0.0038,0.0049,0.9822,0.0011</t>
+  </si>
+  <si>
+    <t>0.0042,0.0200,0.9850,0.0037</t>
+  </si>
+  <si>
+    <t>0.0924,0.0083,0.8606,0.0008</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.9991,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0049,0.9982,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0126,0.0005,0.9828,0.0005</t>
+  </si>
+  <si>
+    <t>0.0006,0.9903,0.0004,0.0473</t>
+  </si>
+  <si>
+    <t>0.0019,0.9980,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9996,0.0002</t>
+  </si>
+  <si>
+    <t>0.0009,0.0255,0.9978,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.0001,0.9982,0.0001</t>
+  </si>
+  <si>
+    <t>0.0210,0.0000,0.9829,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9997,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9990,0.0002</t>
+  </si>
+  <si>
+    <t>0.9973,0.0024,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9880,0.0078,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0050</t>
+  </si>
+  <si>
+    <t>0.9977,0.0010,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9972,0.0018,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9916,0.7158,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0015,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9886,0.9917,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9993,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9930,0.0002,0.0058,0.0000</t>
+  </si>
+  <si>
+    <t>0.0345,0.1217,0.7944,0.0005</t>
+  </si>
+  <si>
+    <t>0.0005,0.0011,0.9993,0.0023</t>
+  </si>
+  <si>
+    <t>0.0000,0.9925,0.9961,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9380,0.8251,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9798,0.9515,0.0001</t>
+  </si>
+  <si>
+    <t>0.0124,0.0001,0.0117,0.9843</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0020,0.9994</t>
+  </si>
+  <si>
+    <t>0.0000,0.9986,0.9944,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9535,0.9981,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9153,0.9419,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.9889,0.0983,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9969,0.9693,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.8427,0.6841,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9977,0.0014,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9991,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0019,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9912,0.0003,0.0045,0.0001</t>
-  </si>
-  <si>
-    <t>0.2611,0.0001,0.8398,0.0000</t>
-  </si>
-  <si>
-    <t>0.7352,0.0004,0.3764,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0001,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.8478,0.0005,0.1960,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9994,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.9984,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.9980,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.5727,0.0002,0.5289,0.0003</t>
-  </si>
-  <si>
-    <t>0.7669,0.0010,0.2666,0.0013</t>
-  </si>
-  <si>
-    <t>0.0019,0.0000,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0043,0.0004,0.9932,0.0002</t>
-  </si>
-  <si>
-    <t>0.2419,0.0000,0.8761,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0088,0.9915,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.7198,0.2850,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0025,0.9996,0.0079</t>
-  </si>
-  <si>
-    <t>0.0009,0.9963,0.0042,0.0001</t>
-  </si>
-  <si>
-    <t>0.9981,0.0003,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0870,0.0063,0.8562,0.0012</t>
-  </si>
-  <si>
-    <t>0.2404,0.8031,0.0029,0.0000</t>
-  </si>
-  <si>
-    <t>0.0059,0.9833,0.0366,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.0013,0.9939,0.0006</t>
-  </si>
-  <si>
-    <t>0.0008,0.0379,0.9954,0.0021</t>
-  </si>
-  <si>
-    <t>0.0363,0.0031,0.9416,0.0007</t>
-  </si>
-  <si>
-    <t>0.0100,0.0000,0.9922,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0048,0.9985,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9811,0.0003,0.6757</t>
-  </si>
-  <si>
-    <t>0.0002,0.9993,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0012,0.0000</t>
+    <t>0.9988,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0004,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0015,0.0014,0.9970,0.0002</t>
+  </si>
+  <si>
+    <t>0.9967,0.0002,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9989,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0067,0.9902,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.0024,0.9952,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9996,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.5289,0.4950,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.4759,0.2390,0.0175,0.0011</t>
+  </si>
+  <si>
+    <t>0.4488,0.0000,0.7395,0.0000</t>
+  </si>
+  <si>
+    <t>0.9962,0.0004,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.7704,0.0070,0.1546,0.0030</t>
+  </si>
+  <si>
+    <t>0.0012,0.0034,0.0001,0.9970</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9981,0.9313,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9987,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.9831,0.0157,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.8449,0.1604,0.0033,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9721,0.9574,0.0002</t>
+  </si>
+  <si>
+    <t>0.0028,0.6192,0.7677,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.0069,0.9957,0.0003</t>
+  </si>
+  <si>
+    <t>0.0014,0.0006,0.9967,0.0001</t>
+  </si>
+  <si>
+    <t>0.9567,0.0011,0.0282,0.0003</t>
+  </si>
+  <si>
+    <t>0.9094,0.0001,0.1659,0.0001</t>
+  </si>
+  <si>
+    <t>0.9847,0.0007,0.0064,0.0001</t>
+  </si>
+  <si>
+    <t>0.0667,0.0001,0.0001,0.9810</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0003,0.9795,0.5413,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0074,0.9749,0.0092,0.0044</t>
+  </si>
+  <si>
+    <t>0.0438,0.9567,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.8937,0.0000,0.0004,0.1971</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.0117,0.9971,0.0245</t>
+  </si>
+  <si>
+    <t>0.9938,0.0001,0.0023,0.0014</t>
+  </si>
+  <si>
+    <t>0.9007,0.0009,0.0412,0.0024</t>
+  </si>
+  <si>
+    <t>0.0380,0.6470,0.0936,0.0008</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0009,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8765,0.0448,0.0105,0.0002</t>
+  </si>
+  <si>
+    <t>0.9525,0.0169,0.0085,0.0001</t>
+  </si>
+  <si>
+    <t>0.9950,0.0011,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0010,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9972,0.0007,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.6869,0.1596,0.0002,0.0015</t>
+  </si>
+  <si>
+    <t>0.0855,0.9490,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.7835,0.3486,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9956,0.0011,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9241,0.0761,0.0024,0.0003</t>
+  </si>
+  <si>
+    <t>0.9986,0.0004,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0019,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.7855,0.2937,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0010,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0002,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0047,0.0027,0.9922,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.0001,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0264,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0002,0.9986,0.0001</t>
   </si>
   <si>
     <t>0.0001,0.0000,0.9997,0.0001</t>
   </si>
   <si>
-    <t>0.0002,0.2041,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0115,0.0000,0.9870,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9997,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.9981,0.0015,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9973,0.0022,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9999,0.0016</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0008,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9601,0.9832,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0109,0.9997,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9956,0.9863,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9969,0.0002,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.9798,0.0038,0.0049,0.0004</t>
-  </si>
-  <si>
-    <t>0.0030,0.0024,0.9942,0.0040</t>
-  </si>
-  <si>
-    <t>0.0000,0.9880,0.9926,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9434,0.9978,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0021,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9931,0.9193,0.0001</t>
-  </si>
-  <si>
-    <t>0.0295,0.0000,0.0008,0.9865</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0000,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.0002,0.9999</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.0067,0.9990</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.9096,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.3821,0.9979,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9381,0.9900,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.8633,0.8669,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9940,0.9612,0.0000</t>
-  </si>
-  <si>
-    <t>0.0031,0.9850,0.0234,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0021,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9966,0.0026,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9968,0.0013,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9990,0.0012,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9977,0.0024,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0002,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.0022,0.0036,0.9941,0.0010</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0029,0.9941,0.0004,0.0009</t>
-  </si>
-  <si>
-    <t>0.0042,0.9944,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9993,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.8579,0.1734,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.8774,0.0035,0.0567,0.0019</t>
-  </si>
-  <si>
-    <t>0.5874,0.0022,0.3993,0.0001</t>
-  </si>
-  <si>
-    <t>0.9309,0.0307,0.0040,0.0005</t>
-  </si>
-  <si>
-    <t>0.8953,0.0006,0.0904,0.0010</t>
-  </si>
-  <si>
-    <t>0.0004,0.0015,0.0000,0.9990</t>
-  </si>
-  <si>
-    <t>0.0001,0.9968,0.7817,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9992,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.8072,0.2328,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.8639,0.1443,0.0027,0.0001</t>
-  </si>
-  <si>
-    <t>0.9952,0.0001,0.0029,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.8600,0.9908,0.0001</t>
-  </si>
-  <si>
-    <t>0.0064,0.4857,0.7603,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0012,0.9979,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0010,0.9983,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9548,0.0102,0.0101,0.0004</t>
-  </si>
-  <si>
-    <t>0.2359,0.0000,0.8725,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0706,0.0004,0.0002,0.9718</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0003,0.9668,0.8757,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0244,0.9664,0.0026,0.0009</t>
-  </si>
-  <si>
-    <t>0.0666,0.9389,0.0018,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.5122,0.0003,0.0183,0.3611</t>
-  </si>
-  <si>
-    <t>0.9976,0.0001,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.0060,0.9962,0.0157</t>
-  </si>
-  <si>
-    <t>0.9990,0.0000,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9564,0.0013,0.0117,0.0051</t>
-  </si>
-  <si>
-    <t>0.3225,0.6261,0.0030,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8583,0.1018,0.0021,0.0005</t>
-  </si>
-  <si>
-    <t>0.9105,0.0514,0.0101,0.0002</t>
-  </si>
-  <si>
-    <t>0.9954,0.0053,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0007,0.0002,0.0001</t>
+    <t>0.0000,0.0001,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.0395,0.0020,0.9526,0.0003</t>
+  </si>
+  <si>
+    <t>0.0196,0.0037,0.9755,0.0006</t>
+  </si>
+  <si>
+    <t>0.0025,0.0003,0.9950,0.0004</t>
+  </si>
+  <si>
+    <t>0.0351,0.0246,0.8978,0.0003</t>
+  </si>
+  <si>
+    <t>0.0177,0.0799,0.7721,0.0006</t>
+  </si>
+  <si>
+    <t>0.9672,0.0007,0.0321,0.0001</t>
+  </si>
+  <si>
+    <t>0.2577,0.0014,0.7027,0.0019</t>
+  </si>
+  <si>
+    <t>0.0596,0.0026,0.9336,0.0005</t>
+  </si>
+  <si>
+    <t>0.0439,0.9737,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9991,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9200,0.1426,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9699,0.0457,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.6770,0.4435,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9928,0.0004,0.0023,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0000,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.5783,0.0128,0.2339,0.0041</t>
+  </si>
+  <si>
+    <t>0.9425,0.0006,0.0695,0.0001</t>
+  </si>
+  <si>
+    <t>0.9714,0.0015,0.0182,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.4549,0.0012,0.5657,0.0004</t>
+  </si>
+  <si>
+    <t>0.0140,0.0013,0.9829,0.0001</t>
+  </si>
+  <si>
+    <t>0.0021,0.0000,0.9980,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0111,0.9948,0.0011</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9925,0.0070,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9991,0.0009,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9780,0.0358,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0017,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0013,0.9993,0.0002</t>
+  </si>
+  <si>
+    <t>0.8425,0.0026,0.0821,0.0007</t>
+  </si>
+  <si>
+    <t>0.9882,0.0013,0.0049,0.0005</t>
+  </si>
+  <si>
+    <t>0.0009,0.0004,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9426,0.9423,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0006,0.9972,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9995,0.0002</t>
+  </si>
+  <si>
+    <t>0.0034,0.0031,0.9904,0.0019</t>
+  </si>
+  <si>
+    <t>0.9651,0.0007,0.0291,0.0003</t>
+  </si>
+  <si>
+    <t>0.0201,0.0003,0.9807,0.0003</t>
+  </si>
+  <si>
+    <t>0.9649,0.0013,0.0208,0.0008</t>
+  </si>
+  <si>
+    <t>0.9888,0.0128,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0015,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0019,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9918,0.0094,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0016,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9993,0.0006,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9964,0.0012,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9930,0.0058,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.7813,0.3555,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.3904,0.7737,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8634,0.0029,0.1281,0.0004</t>
-  </si>
-  <si>
-    <t>0.9557,0.0472,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9875,0.0102,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0018,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9881,0.0013,0.0069,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0024,0.0051,0.9939,0.0002</t>
-  </si>
-  <si>
-    <t>0.0506,0.0000,0.9689,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0494,0.9974,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0015,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.0001,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.0077,0.0005,0.9883,0.0004</t>
-  </si>
-  <si>
-    <t>0.0031,0.0008,0.9959,0.0001</t>
-  </si>
-  <si>
-    <t>0.0261,0.0017,0.9670,0.0003</t>
-  </si>
-  <si>
-    <t>0.0259,0.0694,0.8760,0.0004</t>
-  </si>
-  <si>
-    <t>0.1183,0.0167,0.7897,0.0002</t>
-  </si>
-  <si>
-    <t>0.0930,0.0026,0.9165,0.0004</t>
-  </si>
-  <si>
-    <t>0.4965,0.0225,0.2164,0.0016</t>
-  </si>
-  <si>
-    <t>0.9646,0.0025,0.0167,0.0001</t>
-  </si>
-  <si>
-    <t>0.0020,0.9971,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9990,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.7107,0.4046,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9841,0.0243,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0650,0.9463,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0891,0.7335,0.0442,0.0002</t>
-  </si>
-  <si>
-    <t>0.9974,0.0000,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.8080,0.0063,0.0988,0.0061</t>
-  </si>
-  <si>
-    <t>0.9308,0.0075,0.0336,0.0002</t>
-  </si>
-  <si>
-    <t>0.6934,0.0002,0.4287,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.9991,0.0004</t>
-  </si>
-  <si>
-    <t>0.0087,0.0057,0.9801,0.0004</t>
-  </si>
-  <si>
-    <t>0.0004,0.0219,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.0724,0.0018,0.9406,0.0003</t>
-  </si>
-  <si>
-    <t>0.0056,0.0227,0.9673,0.0006</t>
-  </si>
-  <si>
-    <t>0.9984,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0007,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9802,0.0264,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9986,0.0015,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9859,0.0167,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0019,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0006,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.0003,0.9990,0.0008</t>
-  </si>
-  <si>
-    <t>0.8614,0.0764,0.0146,0.0004</t>
-  </si>
-  <si>
-    <t>0.9600,0.0004,0.0102,0.0066</t>
-  </si>
-  <si>
-    <t>0.0011,0.0010,0.9972,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.1938,0.9791,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0088,0.0016,0.9870,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.0008,0.9985,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0028,0.9980,0.0004</t>
-  </si>
-  <si>
-    <t>0.9680,0.0000,0.0356,0.0006</t>
-  </si>
-  <si>
-    <t>0.9338,0.0032,0.0563,0.0010</t>
-  </si>
-  <si>
-    <t>0.9946,0.0001,0.0028,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0012,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9871,0.0195,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9967,0.0032,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9975,0.0026,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9962,0.0036,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0113,0.0093,0.9749,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0009,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.0005,0.9974,0.0004</t>
-  </si>
-  <si>
-    <t>0.0157,0.0124,0.9576,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.0000,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.6883,0.0001,0.3295,0.0015</t>
-  </si>
-  <si>
-    <t>0.0034,0.0002,0.9933,0.0006</t>
-  </si>
-  <si>
-    <t>0.0015,0.0001,0.9959,0.0005</t>
-  </si>
-  <si>
-    <t>0.9974,0.0000,0.0006,0.0013</t>
-  </si>
-  <si>
-    <t>0.6319,0.0000,0.0000,0.6468</t>
-  </si>
-  <si>
-    <t>0.0186,0.0001,0.0031,0.9831</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9897,0.0002,0.0004,0.0039</t>
+    <t>0.0015,0.0119,0.9931,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.0008,0.9971,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.0020,0.9952,0.0005</t>
+  </si>
+  <si>
+    <t>0.0123,0.1568,0.5925,0.0008</t>
+  </si>
+  <si>
+    <t>0.0011,0.0001,0.9981,0.0003</t>
+  </si>
+  <si>
+    <t>0.0327,0.0001,0.9486,0.0044</t>
+  </si>
+  <si>
+    <t>0.0024,0.0004,0.9952,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9971,0.0059</t>
+  </si>
+  <si>
+    <t>0.9991,0.0000,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.0169,0.0001,0.0000,0.9968</t>
+  </si>
+  <si>
+    <t>0.0026,0.0000,0.0016,0.9971</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.9935,0.0002,0.0011,0.0015</t>
   </si>
 </sst>
 </file>
@@ -2177,7 +2186,7 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
         <v>285</v>
@@ -2460,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>280</v>
+        <v>305</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2474,7 +2483,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2485,10 +2494,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2502,7 +2511,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2516,7 +2525,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2530,7 +2539,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>284</v>
+        <v>310</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2544,7 +2553,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2558,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2572,7 +2581,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2586,7 +2595,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2600,7 +2609,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2614,7 +2623,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2628,7 +2637,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2642,7 +2651,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2656,7 +2665,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2670,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2684,7 +2693,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2698,7 +2707,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2712,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2726,7 +2735,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2740,7 +2749,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2754,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2768,7 +2777,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2782,7 +2791,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2796,7 +2805,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2810,7 +2819,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2824,7 +2833,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2835,10 +2844,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2852,7 +2861,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2866,7 +2875,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2880,7 +2889,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2894,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2908,7 +2917,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2922,7 +2931,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2936,7 +2945,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2950,7 +2959,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2964,7 +2973,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2978,7 +2987,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2992,7 +3001,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3006,7 +3015,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3017,10 +3026,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3034,7 +3043,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3045,10 +3054,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D86" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3062,7 +3071,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3073,10 +3082,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3090,7 +3099,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3104,7 +3113,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3118,7 +3127,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3188,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3216,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3230,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>272</v>
+        <v>355</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3258,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3272,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3286,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>319</v>
+        <v>357</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3300,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3314,7 +3323,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3328,7 +3337,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3342,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3356,7 +3365,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3370,7 +3379,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3398,7 +3407,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3412,7 +3421,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3426,7 +3435,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3440,7 +3449,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3454,7 +3463,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3465,10 +3474,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3479,10 +3488,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3496,7 +3505,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3510,7 +3519,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3524,7 +3533,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3538,7 +3547,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3552,7 +3561,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>284</v>
+        <v>310</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3566,7 +3575,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>280</v>
+        <v>373</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3580,7 +3589,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3594,7 +3603,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3608,7 +3617,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3622,7 +3631,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3636,7 +3645,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>270</v>
+        <v>356</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3650,7 +3659,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>270</v>
+        <v>378</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3664,7 +3673,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>352</v>
+        <v>379</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3678,7 +3687,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3692,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3706,7 +3715,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>355</v>
+        <v>381</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3720,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>355</v>
+        <v>382</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3734,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3748,7 +3757,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3759,10 +3768,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3776,7 +3785,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3790,7 +3799,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3804,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>383</v>
+        <v>356</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3818,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3829,10 +3838,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3846,7 +3855,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3860,7 +3869,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3874,7 +3883,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>337</v>
+        <v>392</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3888,7 +3897,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>337</v>
+        <v>392</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3902,7 +3911,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3916,7 +3925,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3930,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3944,7 +3953,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3958,7 +3967,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>270</v>
+        <v>356</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3972,7 +3981,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3986,7 +3995,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4000,7 +4009,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4014,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4028,7 +4037,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4042,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4056,7 +4065,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4070,7 +4079,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4084,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4098,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4112,7 +4121,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4126,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4140,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>404</v>
+        <v>271</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4154,7 +4163,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4168,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4182,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4196,7 +4205,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4210,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>270</v>
+        <v>356</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4224,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4238,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>270</v>
+        <v>395</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4252,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4266,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4277,10 +4286,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4291,10 +4300,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4308,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4322,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4336,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4350,7 +4359,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4364,7 +4373,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4378,7 +4387,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4392,7 +4401,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4406,7 +4415,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4420,7 +4429,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4434,7 +4443,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4448,7 +4457,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4462,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4476,7 +4485,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4490,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4504,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4518,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4532,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4546,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4560,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4571,10 +4580,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4585,10 +4594,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4599,10 +4608,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4616,7 +4625,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4630,7 +4639,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4644,7 +4653,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4658,7 +4667,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4669,10 +4678,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4683,10 +4692,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4700,7 +4709,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4714,7 +4723,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4728,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4742,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4756,7 +4765,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4770,7 +4779,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4784,7 +4793,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4798,7 +4807,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4812,7 +4821,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4826,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4840,7 +4849,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4854,7 +4863,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4868,7 +4877,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4882,7 +4891,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4896,7 +4905,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4910,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>457</v>
+        <v>355</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4924,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>347</v>
+        <v>378</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4938,7 +4947,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4952,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4966,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4980,7 +4989,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4994,7 +5003,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5005,10 +5014,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5022,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5036,7 +5045,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5050,7 +5059,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>426</v>
+        <v>468</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5064,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5078,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5092,7 +5101,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5103,10 +5112,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5120,7 +5129,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5134,7 +5143,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5148,7 +5157,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5162,7 +5171,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5176,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5190,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>347</v>
+        <v>395</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5204,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>475</v>
+        <v>351</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5218,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5232,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5246,7 +5255,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5260,7 +5269,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5274,7 +5283,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5288,7 +5297,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5302,7 +5311,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5313,10 +5322,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5330,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5344,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5358,7 +5367,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5372,7 +5381,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5386,7 +5395,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5400,7 +5409,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>337</v>
+        <v>491</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5414,7 +5423,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5428,7 +5437,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
